--- a/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-17_Dupla_Materialidade.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-17_Dupla_Materialidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGA_Sistema-de-gestao-ambiental\Registos_SGA_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB73222-CA62-4E47-B981-5B5A4301A290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2FFF01-0623-4C7B-BA82-DE6F6C4117A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2219,7 +2219,7 @@
     <t>Gestor do SGA / EHS (Responsável Ambiental)</t>
   </si>
   <si>
-    <t>Processo 100% elétrico (≈ 7,2 GWh/ano) e 712 t/ano de polímero virgem: as emissões do âmbito 3 a montante superam as do âmbito 2; clientes europeus começam a pedir pegada de carbono.</t>
+    <t>Processo 100% elétrico (≈ 7,8 GWh/ano) e 712 t/ano de polímero virgem: as emissões do âmbito 3 a montante superam as do âmbito 2; clientes europeus começam a pedir pegada de carbono.</t>
   </si>
   <si>
     <t>DM-02</t>
@@ -2873,7 +2873,7 @@
     <t>Impacto negativo</t>
   </si>
   <si>
-    <t>Emissões de GEE do âmbito 2 (≈ 796 tCO2e/ano, location-based) associadas ao consumo de 7,2 GWh de eletricidade e fugas de R410A.</t>
+    <t>Emissões de GEE do âmbito 2 (≈ 860 tCO2e em 2026, location-based) associadas ao consumo de 7,8 GWh de eletricidade e fugas de R410A.</t>
   </si>
   <si>
     <t>Real</t>
@@ -3023,7 +3023,7 @@
     <t>IRO-006</t>
   </si>
   <si>
-    <t>Volatilidade do preço da eletricidade num processo eletrointensivo (≈ 7,2 GWh/ano).</t>
+    <t>Volatilidade do preço da eletricidade num processo eletrointensivo (≈ 7,8 GWh/ano).</t>
   </si>
   <si>
     <t>Custos: +0,03 €/kWh × 7,17 GWh ≈ 215 k€/ano de custo adicional, sem repercussão imediata no preço de venda.</t>
@@ -6632,7 +6632,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4D7D542D-DB3B-4A11-A7B2-36EE0A69B7A8}" type="CELLRANGE">
+                    <a:fld id="{A5F3C422-7E4A-4865-BB6D-A9BB3E5B0ED4}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -6654,7 +6654,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000000-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6665,7 +6665,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{783B6920-E0F5-4C0E-8563-9F61B7B24C5B}" type="CELLRANGE">
+                    <a:fld id="{94338CAF-B4DE-48D6-ABCA-D5C9E82DEEAC}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -6687,7 +6687,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000001-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6714,7 +6714,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000002-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6741,7 +6741,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000003-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6768,7 +6768,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000004-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6779,7 +6779,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F0902D6E-5AD0-41A1-84F7-017A20831B64}" type="CELLRANGE">
+                    <a:fld id="{48F75613-DDB7-423C-BF0D-F2B11E0C9144}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -6801,7 +6801,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000005-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6828,7 +6828,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000006-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6855,7 +6855,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000007-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6882,7 +6882,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000008-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6893,7 +6893,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6918681A-A63A-47F6-801F-4FB101A74FB5}" type="CELLRANGE">
+                    <a:fld id="{CC6246FB-7778-40BD-BB2A-4BB1DD3359A7}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -6915,7 +6915,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000009-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6926,7 +6926,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E5DADAC0-DD5A-460F-A660-631C5DFE6845}" type="CELLRANGE">
+                    <a:fld id="{2DE9DCA4-E115-4E27-9156-F3D28683A2F6}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -6948,7 +6948,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000000A-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -6975,7 +6975,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000000B-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7002,7 +7002,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000000C-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7029,7 +7029,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000000D-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7056,7 +7056,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000000E-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7083,7 +7083,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000000F-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7110,7 +7110,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000010-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7137,7 +7137,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000011-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7148,7 +7148,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1B1AFBD1-D9EA-4530-8FC4-530499E6F6F1}" type="CELLRANGE">
+                    <a:fld id="{85DD3A10-BB45-4DCA-A2C7-1DD3FF5ACDC9}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -7170,7 +7170,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000012-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7197,7 +7197,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000013-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7224,7 +7224,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000014-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7251,7 +7251,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000015-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7278,7 +7278,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000016-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7305,7 +7305,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000017-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7332,7 +7332,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000018-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7359,7 +7359,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000019-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7386,7 +7386,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000001A-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7413,7 +7413,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000001B-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7440,7 +7440,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000001C-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7467,7 +7467,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001D-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000001D-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7494,7 +7494,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000001E-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7521,7 +7521,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000001F-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7548,7 +7548,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000020-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7575,7 +7575,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000021-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7602,7 +7602,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000022-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7629,7 +7629,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000023-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -7983,7 +7983,7 @@
               </c15:datalabelsRange>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A3C7-4759-B6AC-54D3E477B658}"/>
+              <c16:uniqueId val="{00000000-E6BB-427B-B9A7-A76AFACED80A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8046,7 +8046,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000024-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8073,7 +8073,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000025-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8100,7 +8100,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000026-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8111,7 +8111,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{34452BD0-817B-4E1C-AA11-3881494884DB}" type="CELLRANGE">
+                    <a:fld id="{762C2AE8-DC4D-4CC4-8A21-E0A74D43A355}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -8133,7 +8133,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000027-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8160,7 +8160,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000028-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8187,7 +8187,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000029-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8214,7 +8214,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000002A-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8241,7 +8241,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000002B-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8252,7 +8252,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3D1971FC-CE7D-41A4-A37E-ADD11BBF5953}" type="CELLRANGE">
+                    <a:fld id="{779FBE55-AE9A-49A6-8F52-2C71AC30DEDC}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -8274,7 +8274,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002C-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000002C-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8301,7 +8301,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000002D-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8328,7 +8328,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000002E-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8355,7 +8355,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000002F-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8366,7 +8366,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{46FFB729-F945-44D9-958C-1F9A6441C8E3}" type="CELLRANGE">
+                    <a:fld id="{8C7AA493-39FF-4E07-A830-DE0F5EDDF6E4}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -8388,7 +8388,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000030-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8415,7 +8415,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000031-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8442,7 +8442,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000032-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000032-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8469,7 +8469,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000033-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000033-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8496,7 +8496,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000034-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000034-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8507,7 +8507,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{43A9C6AF-DC64-4764-9BF7-99188F07D4EC}" type="CELLRANGE">
+                    <a:fld id="{567E81A9-AF88-4569-A7AB-9316D9261764}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -8529,7 +8529,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000035-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000035-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8556,7 +8556,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000036-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000036-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8583,7 +8583,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000037-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000037-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8610,7 +8610,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000038-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000038-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8637,7 +8637,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000039-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000039-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8664,7 +8664,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003A-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000003A-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8691,7 +8691,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003B-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000003B-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8718,7 +8718,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003C-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000003C-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8745,7 +8745,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003D-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000003D-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8772,7 +8772,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003E-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000003E-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8799,7 +8799,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000003F-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000003F-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8826,7 +8826,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000040-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000040-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8853,7 +8853,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000041-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000041-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8880,7 +8880,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000042-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000042-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8907,7 +8907,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000043-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000043-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8934,7 +8934,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000044-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000044-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8961,7 +8961,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000045-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000045-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -8988,7 +8988,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000046-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000046-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9015,7 +9015,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000047-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000047-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9369,7 +9369,7 @@
               </c15:datalabelsRange>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A3C7-4759-B6AC-54D3E477B658}"/>
+              <c16:uniqueId val="{00000001-E6BB-427B-B9A7-A76AFACED80A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9432,7 +9432,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000048-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000048-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9459,7 +9459,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000049-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000049-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9470,7 +9470,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DEB12EF2-38DA-4683-BA93-1C6BBA4AD484}" type="CELLRANGE">
+                    <a:fld id="{2EB41C80-AD48-4FD4-A01C-0DA6F6073E56}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -9492,7 +9492,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004A-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000004A-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9519,7 +9519,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004B-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000004B-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9546,7 +9546,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004C-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000004C-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9573,7 +9573,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004D-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000004D-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9600,7 +9600,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004E-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000004E-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9627,7 +9627,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000004F-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000004F-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9654,7 +9654,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000050-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000050-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9681,7 +9681,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000051-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000051-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9708,7 +9708,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000052-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000052-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9735,7 +9735,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000053-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000053-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9762,7 +9762,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000054-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000054-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9773,7 +9773,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{06EF7CDA-ED78-4675-8DB9-798935D300DF}" type="CELLRANGE">
+                    <a:fld id="{0D92B371-0147-4C85-9A51-1FC36A8F00DA}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -9795,7 +9795,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000055-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000055-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9822,7 +9822,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000056-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000056-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9849,7 +9849,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000057-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000057-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9876,7 +9876,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000058-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000058-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9903,7 +9903,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000059-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000059-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9930,7 +9930,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000005A-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000005A-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9957,7 +9957,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000005B-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000005B-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -9968,7 +9968,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F187A36F-1967-4AB2-AED5-9B66D786C8A5}" type="CELLRANGE">
+                    <a:fld id="{DC7B4663-A40D-48A1-8AAD-DE4B38F70791}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -9990,7 +9990,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000005C-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000005C-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10001,7 +10001,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{43A594F9-EF1C-4E81-BEAA-07CED0FC2382}" type="CELLRANGE">
+                    <a:fld id="{555F1227-3014-483C-93C6-4F4CA434B377}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -10023,7 +10023,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000005D-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000005D-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10034,7 +10034,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F4B436C4-52C6-48E2-8978-91CAA892CD4A}" type="CELLRANGE">
+                    <a:fld id="{1D6B62DB-E9BD-4B34-8DF1-D9E3983B3F5F}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -10056,7 +10056,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000005E-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000005E-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10067,7 +10067,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{39071A39-5B8A-46B9-89D8-601438CEAC90}" type="CELLRANGE">
+                    <a:fld id="{6DBA3202-BB28-44BA-B2CB-ACAA9857EF1E}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -10089,7 +10089,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000005F-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000005F-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10116,7 +10116,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000060-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000060-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10143,7 +10143,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000061-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000061-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10170,7 +10170,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000062-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000062-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10197,7 +10197,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000063-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000063-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10224,7 +10224,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000064-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000064-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10251,7 +10251,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000065-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000065-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10278,7 +10278,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000066-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000066-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10305,7 +10305,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000067-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000067-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10332,7 +10332,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000068-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000068-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10359,7 +10359,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000069-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000069-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10386,7 +10386,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000006A-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000006A-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10413,7 +10413,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000006B-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000006B-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10767,7 +10767,7 @@
               </c15:datalabelsRange>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-A3C7-4759-B6AC-54D3E477B658}"/>
+              <c16:uniqueId val="{00000002-E6BB-427B-B9A7-A76AFACED80A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10830,7 +10830,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000006C-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000006C-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10857,7 +10857,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000006D-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000006D-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10884,7 +10884,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000006E-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000006E-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10911,7 +10911,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000006F-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000006F-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10922,7 +10922,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B374F75E-B332-42BC-BB6A-B3FA995A33A3}" type="CELLRANGE">
+                    <a:fld id="{E22DFB3D-1874-4504-88CC-644CFA003AFC}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -10944,7 +10944,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000070-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000070-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10971,7 +10971,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000071-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000071-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -10982,7 +10982,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{527FDF5B-EF9F-4F08-A3B5-CED5981357C6}" type="CELLRANGE">
+                    <a:fld id="{417FB1DA-5BA6-4F28-8326-DFB232E7F545}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -11004,7 +11004,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000072-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000072-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11015,7 +11015,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B0FEFF6B-1334-4AEF-931B-B6A0F3FE48D4}" type="CELLRANGE">
+                    <a:fld id="{81A2763E-EB7D-4297-8889-17F5FAB0A318}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -11037,7 +11037,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000073-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000073-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11064,7 +11064,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000074-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000074-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11091,7 +11091,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000075-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000075-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11118,7 +11118,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000076-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000076-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11129,7 +11129,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1CB2B06D-8D7C-4283-86FC-5C9197EF25B3}" type="CELLRANGE">
+                    <a:fld id="{3DD28429-6BD0-48A0-8BD5-E4666ACAC3D3}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -11151,7 +11151,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000077-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000077-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11178,7 +11178,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000078-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000078-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11205,7 +11205,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000079-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000079-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11216,7 +11216,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C0CA7C25-08EC-4AA1-A336-ACFB5941A4D9}" type="CELLRANGE">
+                    <a:fld id="{79386A54-941B-4C1D-83FD-29FC0899BBFC}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -11238,7 +11238,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000007A-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000007A-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11249,7 +11249,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3E445FA5-96BF-49ED-9F7D-9121690C146C}" type="CELLRANGE">
+                    <a:fld id="{449F5B1B-87BA-4496-B4B2-4E89E3A101D1}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -11271,7 +11271,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000007B-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000007B-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11282,7 +11282,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{74BBA0E6-9D98-4C28-846E-FA2E932721CC}" type="CELLRANGE">
+                    <a:fld id="{60A70468-AAC6-472F-A00F-56386ACA3C16}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -11304,7 +11304,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000007C-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000007C-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11331,7 +11331,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000007D-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000007D-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11358,7 +11358,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000007E-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000007E-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11369,7 +11369,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3BB3408E-051D-48DB-BC3A-848967B3151F}" type="CELLRANGE">
+                    <a:fld id="{86664285-F9D4-4674-B3EB-0391004BBB2B}" type="CELLRANGE">
                       <a:rPr lang="pt-PT"/>
                       <a:pPr/>
                       <a:t>[INTERVALODACÉLULA]</a:t>
@@ -11391,7 +11391,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000007F-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000007F-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11418,7 +11418,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000080-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000080-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11445,7 +11445,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000081-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000081-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11472,7 +11472,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000082-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000082-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11499,7 +11499,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000083-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000083-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11526,7 +11526,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000084-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000084-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11553,7 +11553,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000085-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000085-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11580,7 +11580,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000086-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000086-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11607,7 +11607,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000087-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000087-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11634,7 +11634,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000088-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000088-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11661,7 +11661,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000089-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{00000089-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11688,7 +11688,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000008A-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000008A-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11715,7 +11715,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000008B-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000008B-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11742,7 +11742,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000008C-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000008C-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11769,7 +11769,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000008D-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000008D-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11796,7 +11796,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000008E-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000008E-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -11823,7 +11823,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000008F-4F0D-411D-8031-281CC6873671}"/>
+                  <c16:uniqueId val="{0000008F-BB99-4224-907B-B799F655D6C4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -12177,7 +12177,7 @@
               </c15:datalabelsRange>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-A3C7-4759-B6AC-54D3E477B658}"/>
+              <c16:uniqueId val="{00000003-E6BB-427B-B9A7-A76AFACED80A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12231,7 +12231,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-A3C7-4759-B6AC-54D3E477B658}"/>
+              <c16:uniqueId val="{00000004-E6BB-427B-B9A7-A76AFACED80A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12285,7 +12285,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-A3C7-4759-B6AC-54D3E477B658}"/>
+              <c16:uniqueId val="{00000005-E6BB-427B-B9A7-A76AFACED80A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12444,7 +12444,7 @@
             <xdr:cNvPr id="3" name="slc_Pilar">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CB2ED6A-D246-D119-E45B-513B006B1441}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{263BDDDC-D314-E19F-F5AE-31E32627F367}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -12522,7 +12522,7 @@
             <xdr:cNvPr id="4" name="slc_Etapa_Cadeia_Valor">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3293AC3A-DD9F-E57A-725A-F2C3427C01E8}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A8AB5E8-DA3B-EC6F-5EFE-6FB6ED90F2FA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -12600,7 +12600,7 @@
             <xdr:cNvPr id="5" name="slc_Horizonte">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA7922CA-0140-8D46-4CD9-78E809F95B6E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{872B7E4F-1DA3-B474-C5FD-C1758A597AAA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -12678,7 +12678,7 @@
             <xdr:cNvPr id="6" name="slc_Tipo_IRO">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEFEE33F-9574-093A-9980-3EB9D1DD6725}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D18510C-3DD1-2F63-BF61-0066BE5AEC58}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -12756,7 +12756,7 @@
             <xdr:cNvPr id="7" name="slc_Material">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F73E8262-7420-2202-34A5-B2D4724C2334}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{332E1CB1-FB79-15A2-34A7-67149982FD81}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -12834,7 +12834,7 @@
             <xdr:cNvPr id="8" name="slc_Qualidade_Evidencia">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8095E88A-3F96-AC48-FB0C-43C7CE49F71C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12B30B0C-189A-ED35-5D52-1C5F15929559}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -12896,7 +12896,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Aline Meireles" refreshedDate="46295.456829861112" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="87" xr:uid="{0C546E09-8293-4820-BD4C-B34649F5A4B8}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Aline Meireles" refreshedDate="46295.742432638886" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="87" xr:uid="{C8A52D4C-65C2-4DA6-AD7F-B5F4CB5C9846}">
   <cacheSource type="worksheet">
     <worksheetSource name="tbl_dma_iro"/>
   </cacheSource>
@@ -13127,7 +13127,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="354030346"/>
+      <x14:pivotCacheDefinition pivotCacheId="1660871144"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -13143,7 +13143,7 @@
     <x v="0"/>
     <x v="0"/>
     <s v="Impacto"/>
-    <s v="Emissões de GEE do âmbito 2 (≈ 796 tCO2e/ano, location-based) associadas ao consumo de 7,2 GWh de eletricidade e fugas de R410A."/>
+    <s v="Emissões de GEE do âmbito 2 (≈ 860 tCO2e em 2026, location-based) associadas ao consumo de 7,8 GWh de eletricidade e fugas de R410A."/>
     <s v="Real"/>
     <x v="0"/>
     <x v="0"/>
@@ -13398,7 +13398,7 @@
     <x v="0"/>
     <x v="1"/>
     <s v="Financeira"/>
-    <s v="Volatilidade do preço da eletricidade num processo eletrointensivo (≈ 7,2 GWh/ano)."/>
+    <s v="Volatilidade do preço da eletricidade num processo eletrointensivo (≈ 7,8 GWh/ano)."/>
     <m/>
     <x v="0"/>
     <x v="0"/>
@@ -17576,7 +17576,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE9E4025-13DA-477D-AAB8-B4466DB5C42A}" name="pvt_dma_iro" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{612BD501-8C39-4FF7-A0FA-891D926F8D05}" name="pvt_dma_iro" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A94:J132" firstHeaderRow="1" firstDataRow="3" firstDataCol="2"/>
   <pivotFields count="49">
     <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
@@ -17907,12 +17907,12 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Pilar" xr10:uid="{2EDFD6E7-74A5-42F3-9FAF-1D71A83B5C15}" sourceName="Pilar">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Pilar" xr10:uid="{9A6705E4-CA0E-4D65-8F6C-BBFAA40EB020}" sourceName="Pilar">
   <pivotTables>
     <pivotTable tabId="2" name="pvt_dma_iro"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="354030346">
+    <tabular pivotCacheId="1660871144">
       <items count="4">
         <i x="0" s="1"/>
         <i x="2" s="1"/>
@@ -17930,12 +17930,12 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Etapa_Cadeia_Valor" xr10:uid="{F954F14D-6F57-4156-9182-18178E354B4F}" sourceName="Etapa_Cadeia_Valor">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Etapa_Cadeia_Valor" xr10:uid="{E57050CA-A9BC-4B6F-8257-94738A09BAAE}" sourceName="Etapa_Cadeia_Valor">
   <pivotTables>
     <pivotTable tabId="2" name="pvt_dma_iro"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="354030346">
+    <tabular pivotCacheId="1660871144">
       <items count="6">
         <i x="2" s="1"/>
         <i x="4" s="1"/>
@@ -17955,12 +17955,12 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Horizonte" xr10:uid="{886FB6C5-07D0-48D1-9191-1603E7BB04AC}" sourceName="Horizonte">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Horizonte" xr10:uid="{80ED5766-6335-4013-83D0-4077B274B5B5}" sourceName="Horizonte">
   <pivotTables>
     <pivotTable tabId="2" name="pvt_dma_iro"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="354030346">
+    <tabular pivotCacheId="1660871144">
       <items count="4">
         <i x="0" s="1"/>
         <i x="2" s="1"/>
@@ -17978,12 +17978,12 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache4.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Tipo_IRO" xr10:uid="{F828998B-35F8-4E5C-A2F6-F758FFCD21D9}" sourceName="Tipo_IRO">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Tipo_IRO" xr10:uid="{40B1EA2F-C51C-4B46-82B4-6EC33E99ED6A}" sourceName="Tipo_IRO">
   <pivotTables>
     <pivotTable tabId="2" name="pvt_dma_iro"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="354030346">
+    <tabular pivotCacheId="1660871144">
       <items count="5">
         <i x="0" s="1"/>
         <i x="3" s="1"/>
@@ -18002,12 +18002,12 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache5.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Material" xr10:uid="{31F28A31-B88E-4D18-9AF4-383B8CA405E6}" sourceName="Material">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Material" xr10:uid="{06457CA8-24E2-44D0-AFE5-B45C36ADB6F8}" sourceName="Material">
   <pivotTables>
     <pivotTable tabId="2" name="pvt_dma_iro"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="354030346">
+    <tabular pivotCacheId="1660871144">
       <items count="3">
         <i x="1" s="1"/>
         <i x="0" s="1"/>
@@ -18024,12 +18024,12 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache6.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Qualidade_Evidencia" xr10:uid="{FE025815-FED1-4085-AEB5-997965E2C920}" sourceName="Qualidade_Evidencia">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãoDeDados_Qualidade_Evidencia" xr10:uid="{B7C41BFB-41C2-4B2B-9E28-39FB6A773C1A}" sourceName="Qualidade_Evidencia">
   <pivotTables>
     <pivotTable tabId="2" name="pvt_dma_iro"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="354030346">
+    <tabular pivotCacheId="1660871144">
       <items count="4">
         <i x="0" s="1"/>
         <i x="1" s="1"/>
@@ -18048,12 +18048,12 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="slc_Pilar" xr10:uid="{2F30C634-AB0A-47B8-A06D-C292109FC127}" cache="SegmentaçãoDeDados_Pilar" caption="Pilar" rowHeight="234950"/>
-  <slicer name="slc_Etapa_Cadeia_Valor" xr10:uid="{26CEBC0D-C8E3-4BA7-92D7-49F596071C94}" cache="SegmentaçãoDeDados_Etapa_Cadeia_Valor" caption="Etapa da cadeia de valor" rowHeight="234950"/>
-  <slicer name="slc_Horizonte" xr10:uid="{78654F64-84FF-449A-83A9-FDA93518AB39}" cache="SegmentaçãoDeDados_Horizonte" caption="Horizonte" rowHeight="234950"/>
-  <slicer name="slc_Tipo_IRO" xr10:uid="{1383EE57-1393-444F-860D-8AC01EF3157E}" cache="SegmentaçãoDeDados_Tipo_IRO" caption="Tipo de IRO" rowHeight="234950"/>
-  <slicer name="slc_Material" xr10:uid="{781199C4-32AE-4517-939C-FBEBE26828DE}" cache="SegmentaçãoDeDados_Material" caption="Material" rowHeight="234950"/>
-  <slicer name="slc_Qualidade_Evidencia" xr10:uid="{78755995-BBF0-4854-AB66-006F976123BF}" cache="SegmentaçãoDeDados_Qualidade_Evidencia" caption="Qualidade da evidência" rowHeight="234950"/>
+  <slicer name="slc_Pilar" xr10:uid="{CADD84DF-C69C-411B-A380-0448595E81F5}" cache="SegmentaçãoDeDados_Pilar" caption="Pilar" rowHeight="234950"/>
+  <slicer name="slc_Etapa_Cadeia_Valor" xr10:uid="{C5ED3C15-BABF-4503-9EA5-A73BEAECF827}" cache="SegmentaçãoDeDados_Etapa_Cadeia_Valor" caption="Etapa da cadeia de valor" rowHeight="234950"/>
+  <slicer name="slc_Horizonte" xr10:uid="{3F7790FA-9C1D-4A2C-B87D-EFB52176A660}" cache="SegmentaçãoDeDados_Horizonte" caption="Horizonte" rowHeight="234950"/>
+  <slicer name="slc_Tipo_IRO" xr10:uid="{774D8B6A-1FF4-40FE-9668-A286AA6058C5}" cache="SegmentaçãoDeDados_Tipo_IRO" caption="Tipo de IRO" rowHeight="234950"/>
+  <slicer name="slc_Material" xr10:uid="{92F32C80-F24E-4732-BD3C-15CABECBE29A}" cache="SegmentaçãoDeDados_Material" caption="Material" rowHeight="234950"/>
+  <slicer name="slc_Qualidade_Evidencia" xr10:uid="{463D10A7-DC47-4DB2-8B56-B9CC07933BF1}" cache="SegmentaçãoDeDados_Qualidade_Evidencia" caption="Qualidade da evidência" rowHeight="234950"/>
 </slicers>
 </file>
 
